--- a/SAM_Opportunities_Report_20260615_PM.xlsx
+++ b/SAM_Opportunities_Report_20260615_PM.xlsx
@@ -14,10 +14,10 @@
     <sheet name="🔧 Specialty Pipeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -855,7 +855,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>139</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F26" s="26" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F27" s="27" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F36" s="26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F38" s="26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N93"/>
+  <dimension ref="B2:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1336,7 +1336,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>All open Solicitations sorted by urgency  ·  88 records  ·  As of June 15, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
+          <t>All open Solicitations sorted by urgency  ·  90 records  ·  As of June 15, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D37" s="36" t="inlineStr">
         <is>
-          <t>NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
+          <t>Z--NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="D85" s="36" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>W9127826RA059</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="K86" s="43" t="inlineStr">
@@ -6836,67 +6836,67 @@
       </c>
     </row>
     <row r="87" ht="32" customHeight="1">
-      <c r="B87" s="39" t="inlineStr">
+      <c r="B87" s="23" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="C87" s="21" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="D87" s="28" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="E87" s="21" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="G87" s="40" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H87" s="21" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="I87" s="21" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="J87" s="21" t="inlineStr">
-        <is>
-          <t>37d</t>
-        </is>
-      </c>
-      <c r="K87" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
-        </is>
-      </c>
-      <c r="L87" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M87" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N87" s="42" t="inlineStr">
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>75F40126R00051</t>
+        </is>
+      </c>
+      <c r="D87" s="36" t="inlineStr">
+        <is>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>Jefferson, Arkansas</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="23" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="J87" s="23" t="inlineStr">
+        <is>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K87" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L87" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M87" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N87" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6910,22 +6910,22 @@
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>FA302226Q0009</t>
+          <t>W9127826RA059</t>
         </is>
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable B230 to B9511</t>
+          <t>Water Tank Storage</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
@@ -6940,17 +6940,17 @@
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="J88" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K88" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="K88" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L88" s="17" t="inlineStr">
@@ -6977,22 +6977,22 @@
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>36C25726B0006</t>
+          <t>36C25626R0015</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
         <is>
-          <t>Z2DA--519-20-200 VABS Replace Boiler Plant Solicitation 36C25726B0006</t>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>Big Spring, Texas</t>
+          <t>Fayetteville, Arkansas</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G89" s="40" t="inlineStr">
@@ -7002,22 +7002,22 @@
       </c>
       <c r="H89" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$15.0M</t>
         </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="J89" s="21" t="inlineStr">
         <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K89" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>37d</t>
+        </is>
+      </c>
+      <c r="K89" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="L89" s="21" t="inlineStr">
@@ -7044,22 +7044,22 @@
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>W912P826BA041</t>
+          <t>FA302226Q0009</t>
         </is>
       </c>
       <c r="D90" s="33" t="inlineStr">
         <is>
-          <t>West Shore Lake Pontchartrain, Louisiana, Hurricane and Storm Damage Risk Reduction Project, WSLP-103A Levee, Floodwall and Gate, Sta. 819+87 B/L to Sta. 827+95 B/L, St. John the Baptist Parish, Louisiana ED 24-025</t>
+          <t>Fiber Optic Cable B230 to B9511</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>New Orleans, Louisiana</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -7104,47 +7104,47 @@
       </c>
     </row>
     <row r="91" ht="32" customHeight="1">
-      <c r="B91" s="23" t="inlineStr">
+      <c r="B91" s="39" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>140P8426Q0035</t>
-        </is>
-      </c>
-      <c r="D91" s="36" t="inlineStr">
-        <is>
-          <t>Y--Grade and Pave, Lassen Volcanic NP</t>
-        </is>
-      </c>
-      <c r="E91" s="23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I91" s="23" t="inlineStr">
+      <c r="C91" s="21" t="inlineStr">
+        <is>
+          <t>36C25726B0006</t>
+        </is>
+      </c>
+      <c r="D91" s="28" t="inlineStr">
+        <is>
+          <t>Z2DA--519-20-200 VABS Replace Boiler Plant Solicitation 36C25726B0006</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="inlineStr">
+        <is>
+          <t>Big Spring, Texas</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>237130</t>
+        </is>
+      </c>
+      <c r="G91" s="40" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H91" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="21" t="inlineStr">
         <is>
           <t>Jun 16, 2026</t>
         </is>
       </c>
-      <c r="J91" s="23" t="inlineStr">
+      <c r="J91" s="21" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
@@ -7154,17 +7154,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L91" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M91" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N91" s="38" t="inlineStr">
+      <c r="L91" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -7178,134 +7178,268 @@
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
+          <t>W912P826BA041</t>
+        </is>
+      </c>
+      <c r="D92" s="33" t="inlineStr">
+        <is>
+          <t>West Shore Lake Pontchartrain, Louisiana, Hurricane and Storm Damage Risk Reduction Project, WSLP-103A Levee, Floodwall and Gate, Sta. 819+87 B/L to Sta. 827+95 B/L, St. John the Baptist Parish, Louisiana ED 24-025</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>New Orleans, Louisiana</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>Jun 16, 2026</t>
+        </is>
+      </c>
+      <c r="J92" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K92" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L92" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>140P8426Q0035</t>
+        </is>
+      </c>
+      <c r="D93" s="36" t="inlineStr">
+        <is>
+          <t>Y--Grade and Pave, Lassen Volcanic NP</t>
+        </is>
+      </c>
+      <c r="E93" s="23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="23" t="inlineStr">
+        <is>
+          <t>Jun 16, 2026</t>
+        </is>
+      </c>
+      <c r="J93" s="23" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K93" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L93" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
           <t>140P6426B0002</t>
         </is>
       </c>
-      <c r="D92" s="33" t="inlineStr">
+      <c r="D94" s="33" t="inlineStr">
         <is>
           <t>Z--Trail Replacement</t>
         </is>
       </c>
-      <c r="E92" s="17" t="inlineStr">
+      <c r="E94" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F92" s="17" t="inlineStr">
+      <c r="F94" s="17" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H92" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
         <is>
           <t>Jun 16, 2026</t>
         </is>
       </c>
-      <c r="J92" s="17" t="inlineStr">
+      <c r="J94" s="17" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K92" s="18" t="inlineStr">
+      <c r="K94" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L92" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M92" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N92" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="32" customHeight="1">
-      <c r="B93" s="39" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C93" s="21" t="inlineStr">
+      <c r="L94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M94" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="B95" s="39" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="inlineStr">
         <is>
           <t>W91RUS26RA009</t>
         </is>
       </c>
-      <c r="D93" s="28" t="inlineStr">
+      <c r="D95" s="28" t="inlineStr">
         <is>
           <t>Range 13 ARF Upgrade</t>
         </is>
       </c>
-      <c r="E93" s="21" t="inlineStr">
+      <c r="E95" s="21" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F93" s="21" t="inlineStr">
+      <c r="F95" s="21" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="G93" s="40" t="inlineStr">
+      <c r="G95" s="40" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="H93" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I93" s="21" t="inlineStr">
+      <c r="H95" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="21" t="inlineStr">
         <is>
           <t>Jun 16, 2026</t>
         </is>
       </c>
-      <c r="J93" s="21" t="inlineStr">
+      <c r="J95" s="21" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K93" s="18" t="inlineStr">
+      <c r="K95" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L93" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M93" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N93" s="42" t="inlineStr">
+      <c r="L95" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M95" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:N93"/>
+  <autoFilter ref="B5:N95"/>
   <mergeCells count="2">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -7399,6 +7533,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N95" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7411,7 +7547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K52"/>
+  <dimension ref="B2:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7439,7 +7575,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Early-stage opportunities to monitor  ·  47 records  (7 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
+          <t>Early-stage opportunities to monitor  ·  49 records  (7 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
         </is>
       </c>
     </row>
@@ -8487,22 +8623,22 @@
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>W912DR26BA007</t>
         </is>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -8512,17 +8648,17 @@
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -8539,22 +8675,22 @@
     <row r="26" ht="32" customHeight="1">
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>W912WJ26QA119</t>
+          <t>75H70126R00029</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -8564,17 +8700,17 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>45d</t>
         </is>
       </c>
       <c r="J26" s="17" t="inlineStr">
@@ -8591,22 +8727,22 @@
     <row r="27" ht="32" customHeight="1">
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>140P6026Q0052</t>
+          <t>75H70126R00030</t>
         </is>
       </c>
       <c r="C27" s="36" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -8616,17 +8752,17 @@
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -8643,12 +8779,12 @@
     <row r="28" ht="32" customHeight="1">
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>12445526Q0069</t>
+          <t>W912WJ26QA119</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
@@ -8668,22 +8804,22 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>$25K</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>8d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
@@ -8695,22 +8831,22 @@
     <row r="29" ht="32" customHeight="1">
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>W9127826RA025</t>
+          <t>140P6026Q0052</t>
         </is>
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>Phillips Parkway Haul Route</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>Cape Canaveral, Florida</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
@@ -8720,22 +8856,22 @@
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
@@ -8747,12 +8883,12 @@
     <row r="30" ht="32" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>12445526Q0069</t>
         </is>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
@@ -8762,7 +8898,7 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -8772,22 +8908,22 @@
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$25K</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
@@ -8799,22 +8935,22 @@
     <row r="31" ht="32" customHeight="1">
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>W9127826RA025</t>
         </is>
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Cape Canaveral, Florida</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -8829,12 +8965,12 @@
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -8851,12 +8987,12 @@
     <row r="32" ht="32" customHeight="1">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -8866,7 +9002,7 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
@@ -8903,12 +9039,12 @@
     <row r="33" ht="32" customHeight="1">
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>SP470525R002026</t>
         </is>
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -8918,7 +9054,7 @@
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
@@ -8933,17 +9069,17 @@
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -8955,12 +9091,12 @@
     <row r="34" ht="32" customHeight="1">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>36C25226Q0426</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -8970,7 +9106,7 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -8985,12 +9121,12 @@
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
@@ -9007,12 +9143,12 @@
     <row r="35" ht="32" customHeight="1">
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -9022,7 +9158,7 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
@@ -9037,12 +9173,12 @@
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -9059,12 +9195,12 @@
     <row r="36" ht="32" customHeight="1">
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>W912BU26BA026</t>
+          <t>36C25226Q0426</t>
         </is>
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>Absecon Island Outfalls Repair</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
@@ -9074,7 +9210,7 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -9089,12 +9225,12 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J36" s="17" t="inlineStr">
@@ -9111,22 +9247,22 @@
     <row r="37" ht="32" customHeight="1">
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>FA301626FB0001</t>
+          <t>W912BU26BA026</t>
         </is>
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>Repair Carswell Ave.</t>
+          <t>Absecon Island Outfalls Repair</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>DWG, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
@@ -9141,12 +9277,12 @@
       </c>
       <c r="H37" s="23" t="inlineStr">
         <is>
-          <t>Jun 17, 2026</t>
+          <t>Jun 16, 2026</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -9163,22 +9299,22 @@
     <row r="38" ht="32" customHeight="1">
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>W911WN26RA011</t>
+          <t>FA301626FB0001</t>
         </is>
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
+          <t>Repair Carswell Ave.</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>DWG, Texas</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
@@ -9193,12 +9329,12 @@
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jun 17, 2026</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
@@ -9215,12 +9351,12 @@
     <row r="39" ht="32" customHeight="1">
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>140L2626R0004</t>
+          <t>W911WN26RA011</t>
         </is>
       </c>
       <c r="C39" s="36" t="inlineStr">
         <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
+          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
@@ -9245,12 +9381,12 @@
       </c>
       <c r="H39" s="23" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I39" s="23" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J39" s="23" t="inlineStr">
@@ -9267,12 +9403,12 @@
     <row r="40" ht="32" customHeight="1">
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0032</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>Y--Indian Springs Vault Toilet</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
@@ -9319,12 +9455,12 @@
     <row r="41" ht="32" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>Y--Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -9334,7 +9470,7 @@
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
@@ -9349,12 +9485,12 @@
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -9371,12 +9507,12 @@
     <row r="42" ht="32" customHeight="1">
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
@@ -9386,7 +9522,7 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
@@ -9423,12 +9559,12 @@
     <row r="43" ht="32" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
@@ -9453,12 +9589,12 @@
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I43" s="23" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J43" s="23" t="inlineStr">
@@ -9475,22 +9611,22 @@
     <row r="44" ht="32" customHeight="1">
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>W912EE26RA015</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -9505,12 +9641,12 @@
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J44" s="17" t="inlineStr">
@@ -9527,17 +9663,17 @@
     <row r="45" ht="32" customHeight="1">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>36C24526Q0576</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C45" s="36" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
@@ -9557,12 +9693,12 @@
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I45" s="23" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J45" s="23" t="inlineStr">
@@ -9579,22 +9715,22 @@
     <row r="46" ht="32" customHeight="1">
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>36C24526Q0576</t>
         </is>
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
@@ -9609,12 +9745,12 @@
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>38d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J46" s="17" t="inlineStr">
@@ -9631,12 +9767,12 @@
     <row r="47" ht="32" customHeight="1">
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C47" s="36" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -9646,7 +9782,7 @@
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
@@ -9683,12 +9819,12 @@
     <row r="48" ht="32" customHeight="1">
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -9698,7 +9834,7 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
@@ -9735,22 +9871,22 @@
     <row r="49" ht="32" customHeight="1">
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>140P6326B0008</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C49" s="36" t="inlineStr">
         <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>Medora, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
@@ -9765,12 +9901,12 @@
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I49" s="23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>38d</t>
         </is>
       </c>
       <c r="J49" s="23" t="inlineStr">
@@ -9787,17 +9923,17 @@
     <row r="50" ht="32" customHeight="1">
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>140P8526Q0083</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
@@ -9817,12 +9953,12 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J50" s="17" t="inlineStr">
@@ -9839,12 +9975,12 @@
     <row r="51" ht="32" customHeight="1">
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>140P9726Q0046</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C51" s="36" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
@@ -9854,7 +9990,7 @@
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
@@ -9891,57 +10027,161 @@
     <row r="52" ht="32" customHeight="1">
       <c r="B52" s="17" t="inlineStr">
         <is>
+          <t>140P9726Q0046</t>
+        </is>
+      </c>
+      <c r="C52" s="33" t="inlineStr">
+        <is>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>9d</t>
+        </is>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
           <t>W50S85-26-B-A007</t>
         </is>
       </c>
-      <c r="C52" s="33" t="inlineStr">
+      <c r="C53" s="36" t="inlineStr">
         <is>
           <t>Feeder #7 Repair</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D53" s="23" t="inlineStr">
         <is>
           <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="17" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I52" s="17" t="inlineStr">
+      <c r="I53" s="23" t="inlineStr">
         <is>
           <t>14d</t>
         </is>
       </c>
-      <c r="J52" s="17" t="inlineStr">
+      <c r="J53" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K52" s="17" t="inlineStr">
+      <c r="K53" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>W912DQ26QA063</t>
+        </is>
+      </c>
+      <c r="C54" s="33" t="inlineStr">
+        <is>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Stockton, Missouri</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K52"/>
+  <autoFilter ref="B5:K54"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -9957,7 +10197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K140"/>
+  <dimension ref="B2:K144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9985,7 +10225,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Complete data  ·  135 records  ·  June 15, 2026</t>
+          <t>Complete data  ·  139 records  ·  June 15, 2026</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11902,7 @@
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
+          <t>Z--NM DEXTER NFHTC POND LINER 12B &amp; 13B</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
@@ -14153,12 +14393,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="B85" s="23" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="C85" s="36" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D85" s="23" t="inlineStr">
@@ -14168,7 +14408,7 @@
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
@@ -14205,12 +14445,12 @@
     <row r="86" ht="28" customHeight="1">
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>W9127826RA059</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
@@ -14235,12 +14475,12 @@
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
@@ -14255,52 +14495,52 @@
       </c>
     </row>
     <row r="87" ht="28" customHeight="1">
-      <c r="B87" s="21" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="C87" s="28" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="E87" s="21" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G87" s="21" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="H87" s="21" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="I87" s="21" t="inlineStr">
-        <is>
-          <t>37d</t>
-        </is>
-      </c>
-      <c r="J87" s="21" t="inlineStr">
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>75F40126R00051</t>
+        </is>
+      </c>
+      <c r="C87" s="36" t="inlineStr">
+        <is>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="inlineStr">
+        <is>
+          <t>Jefferson, Arkansas</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="I87" s="23" t="inlineStr">
+        <is>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="J87" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K87" s="42" t="inlineStr">
+      <c r="K87" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14309,22 +14549,22 @@
     <row r="88" ht="28" customHeight="1">
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>FA302226Q0009</t>
+          <t>W9127826RA059</t>
         </is>
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable B230 to B9511</t>
+          <t>Water Tank Storage</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -14339,12 +14579,12 @@
       </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="J88" s="17" t="inlineStr">
@@ -14361,22 +14601,22 @@
     <row r="89" ht="28" customHeight="1">
       <c r="B89" s="21" t="inlineStr">
         <is>
-          <t>36C25726B0006</t>
+          <t>36C25626R0015</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
         <is>
-          <t>Z2DA--519-20-200 VABS Replace Boiler Plant Solicitation 36C25726B0006</t>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>Big Spring, Texas</t>
+          <t>Fayetteville, Arkansas</t>
         </is>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
@@ -14386,17 +14626,17 @@
       </c>
       <c r="G89" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$15.0M</t>
         </is>
       </c>
       <c r="H89" s="21" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>37d</t>
         </is>
       </c>
       <c r="J89" s="21" t="inlineStr">
@@ -14413,22 +14653,22 @@
     <row r="90" ht="28" customHeight="1">
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>W912P826BA041</t>
+          <t>FA302226Q0009</t>
         </is>
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
-          <t>West Shore Lake Pontchartrain, Louisiana, Hurricane and Storm Damage Risk Reduction Project, WSLP-103A Levee, Floodwall and Gate, Sta. 819+87 B/L to Sta. 827+95 B/L, St. John the Baptist Parish, Louisiana ED 24-025</t>
+          <t>Fiber Optic Cable B230 to B9511</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>New Orleans, Louisiana</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -14463,52 +14703,52 @@
       </c>
     </row>
     <row r="91" ht="28" customHeight="1">
-      <c r="B91" s="23" t="inlineStr">
-        <is>
-          <t>140P8426Q0035</t>
-        </is>
-      </c>
-      <c r="C91" s="36" t="inlineStr">
-        <is>
-          <t>Y--Grade and Pave, Lassen Volcanic NP</t>
-        </is>
-      </c>
-      <c r="D91" s="23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E91" s="23" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
+      <c r="B91" s="21" t="inlineStr">
+        <is>
+          <t>36C25726B0006</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="inlineStr">
+        <is>
+          <t>Z2DA--519-20-200 VABS Replace Boiler Plant Solicitation 36C25726B0006</t>
+        </is>
+      </c>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>Big Spring, Texas</t>
+        </is>
+      </c>
+      <c r="E91" s="21" t="inlineStr">
+        <is>
+          <t>237130</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G91" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="21" t="inlineStr">
         <is>
           <t>Jun 16, 2026</t>
         </is>
       </c>
-      <c r="I91" s="23" t="inlineStr">
+      <c r="I91" s="21" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="J91" s="23" t="inlineStr">
+      <c r="J91" s="21" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K91" s="38" t="inlineStr">
+      <c r="K91" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14517,102 +14757,102 @@
     <row r="92" ht="28" customHeight="1">
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0002</t>
+          <t>W912P826BA041</t>
         </is>
       </c>
       <c r="C92" s="33" t="inlineStr">
         <is>
-          <t>Z--Trail Replacement</t>
+          <t>West Shore Lake Pontchartrain, Louisiana, Hurricane and Storm Damage Risk Reduction Project, WSLP-103A Levee, Floodwall and Gate, Sta. 819+87 B/L to Sta. 827+95 B/L, St. John the Baptist Parish, Louisiana ED 24-025</t>
         </is>
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
+          <t>New Orleans, Louisiana</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>Jun 16, 2026</t>
+        </is>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="J92" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K92" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>140P8426Q0035</t>
+        </is>
+      </c>
+      <c r="C93" s="36" t="inlineStr">
+        <is>
+          <t>Y--Grade and Pave, Lassen Volcanic NP</t>
+        </is>
+      </c>
+      <c r="D93" s="23" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E92" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F92" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H92" s="17" t="inlineStr">
+      <c r="E93" s="23" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
         <is>
           <t>Jun 16, 2026</t>
         </is>
       </c>
-      <c r="I92" s="17" t="inlineStr">
+      <c r="I93" s="23" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="J92" s="17" t="inlineStr">
+      <c r="J93" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K92" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="B93" s="21" t="inlineStr">
-        <is>
-          <t>W91RUS26RA009</t>
-        </is>
-      </c>
-      <c r="C93" s="28" t="inlineStr">
-        <is>
-          <t>Range 13 ARF Upgrade</t>
-        </is>
-      </c>
-      <c r="D93" s="21" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E93" s="21" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F93" s="21" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G93" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="21" t="inlineStr">
-        <is>
-          <t>Jun 16, 2026</t>
-        </is>
-      </c>
-      <c r="I93" s="21" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J93" s="21" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K93" s="42" t="inlineStr">
+      <c r="K93" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14621,22 +14861,22 @@
     <row r="94" ht="28" customHeight="1">
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>FA301626FB0001</t>
+          <t>140P6426B0002</t>
         </is>
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
-          <t>Repair Carswell Ave.</t>
+          <t>Z--Trail Replacement</t>
         </is>
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t>DWG, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -14651,17 +14891,17 @@
       </c>
       <c r="H94" s="17" t="inlineStr">
         <is>
-          <t>Jun 17, 2026</t>
+          <t>Jun 16, 2026</t>
         </is>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K94" s="35" t="inlineStr">
@@ -14673,206 +14913,206 @@
     <row r="95" ht="28" customHeight="1">
       <c r="B95" s="21" t="inlineStr">
         <is>
+          <t>W91RUS26RA009</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="inlineStr">
+        <is>
+          <t>Range 13 ARF Upgrade</t>
+        </is>
+      </c>
+      <c r="D95" s="21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E95" s="21" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G95" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" s="21" t="inlineStr">
+        <is>
+          <t>Jun 16, 2026</t>
+        </is>
+      </c>
+      <c r="I95" s="21" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="J95" s="21" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K95" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>FA301626FB0001</t>
+        </is>
+      </c>
+      <c r="C96" s="33" t="inlineStr">
+        <is>
+          <t>Repair Carswell Ave.</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>DWG, Texas</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>Jun 17, 2026</t>
+        </is>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="J96" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K96" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="B97" s="21" t="inlineStr">
+        <is>
           <t>36C25026B0050</t>
         </is>
       </c>
-      <c r="C95" s="28" t="inlineStr">
+      <c r="C97" s="28" t="inlineStr">
         <is>
           <t>Z1DA--Project No. 552-26-202 - Replace Overhead Paging System</t>
         </is>
       </c>
-      <c r="D95" s="21" t="inlineStr">
+      <c r="D97" s="21" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E95" s="21" t="inlineStr">
+      <c r="E97" s="21" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F95" s="21" t="inlineStr">
+      <c r="F97" s="21" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G95" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H95" s="21" t="inlineStr">
+      <c r="G97" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="21" t="inlineStr">
         <is>
           <t>Jun 17, 2026</t>
         </is>
       </c>
-      <c r="I95" s="21" t="inlineStr">
+      <c r="I97" s="21" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="J95" s="21" t="inlineStr">
+      <c r="J97" s="21" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K95" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="B96" s="21" t="inlineStr">
+      <c r="K97" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="B98" s="21" t="inlineStr">
         <is>
           <t>36C25026B0045</t>
         </is>
       </c>
-      <c r="C96" s="28" t="inlineStr">
+      <c r="C98" s="28" t="inlineStr">
         <is>
           <t>Z2LC--Campus Sinkhole Repair  552-26-506</t>
         </is>
       </c>
-      <c r="D96" s="21" t="inlineStr">
+      <c r="D98" s="21" t="inlineStr">
         <is>
           <t>Dayton, Ohio</t>
         </is>
       </c>
-      <c r="E96" s="21" t="inlineStr">
+      <c r="E98" s="21" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F96" s="21" t="inlineStr">
+      <c r="F98" s="21" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G96" s="21" t="inlineStr">
+      <c r="G98" s="21" t="inlineStr">
         <is>
           <t>$750K</t>
         </is>
       </c>
-      <c r="H96" s="21" t="inlineStr">
+      <c r="H98" s="21" t="inlineStr">
         <is>
           <t>Jun 18, 2026</t>
         </is>
       </c>
-      <c r="I96" s="21" t="inlineStr">
+      <c r="I98" s="21" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="J96" s="21" t="inlineStr">
+      <c r="J98" s="21" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K96" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="28" customHeight="1">
-      <c r="B97" s="23" t="inlineStr">
-        <is>
-          <t>W911WN26RA011</t>
-        </is>
-      </c>
-      <c r="C97" s="36" t="inlineStr">
-        <is>
-          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
-        </is>
-      </c>
-      <c r="D97" s="23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E97" s="23" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F97" s="23" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" s="23" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I97" s="23" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="J97" s="23" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K97" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="28" customHeight="1">
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>140P6026Q0052</t>
-        </is>
-      </c>
-      <c r="C98" s="33" t="inlineStr">
-        <is>
-          <t>Z--WACO Emergency Generator</t>
-        </is>
-      </c>
-      <c r="D98" s="17" t="inlineStr">
-        <is>
-          <t>Waco, Texas</t>
-        </is>
-      </c>
-      <c r="E98" s="17" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F98" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G98" s="17" t="inlineStr">
-        <is>
-          <t>$62K</t>
-        </is>
-      </c>
-      <c r="H98" s="17" t="inlineStr">
-        <is>
-          <t>Jun 18, 2026</t>
-        </is>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="J98" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K98" s="35" t="inlineStr">
+      <c r="K98" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14881,12 +15121,12 @@
     <row r="99" ht="28" customHeight="1">
       <c r="B99" s="23" t="inlineStr">
         <is>
-          <t>36C25226Q0426</t>
+          <t>W911WN26RA011</t>
         </is>
       </c>
       <c r="C99" s="36" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>Install 4 Corners Hydraulics at Dashields Locks and Dam</t>
         </is>
       </c>
       <c r="D99" s="23" t="inlineStr">
@@ -14896,7 +15136,7 @@
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
@@ -14911,12 +15151,12 @@
       </c>
       <c r="H99" s="23" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I99" s="23" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J99" s="23" t="inlineStr">
@@ -14933,22 +15173,22 @@
     <row r="100" ht="28" customHeight="1">
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>36C24526Q0576</t>
+          <t>140P6026Q0052</t>
         </is>
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
@@ -14958,17 +15198,17 @@
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J100" s="17" t="inlineStr">
@@ -14985,22 +15225,22 @@
     <row r="101" ht="28" customHeight="1">
       <c r="B101" s="23" t="inlineStr">
         <is>
-          <t>FDA-PRESOL-132892</t>
+          <t>36C25226Q0426</t>
         </is>
       </c>
       <c r="C101" s="36" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
@@ -15010,7 +15250,7 @@
       </c>
       <c r="G101" s="23" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H101" s="23" t="inlineStr">
@@ -15037,22 +15277,22 @@
     <row r="102" ht="28" customHeight="1">
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>36C24526Q0576</t>
         </is>
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
@@ -15067,12 +15307,12 @@
       </c>
       <c r="H102" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J102" s="17" t="inlineStr">
@@ -15089,22 +15329,22 @@
     <row r="103" ht="28" customHeight="1">
       <c r="B103" s="23" t="inlineStr">
         <is>
-          <t>W50S7X-26-B-A003</t>
+          <t>FDA-PRESOL-132892</t>
         </is>
       </c>
       <c r="C103" s="36" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D103" s="23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
@@ -15114,17 +15354,17 @@
       </c>
       <c r="G103" s="23" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="H103" s="23" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="I103" s="23" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="J103" s="23" t="inlineStr">
@@ -15141,17 +15381,17 @@
     <row r="104" ht="28" customHeight="1">
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>GROUP1-24-R-W001</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
@@ -15166,17 +15406,17 @@
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>$17.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
-          <t>8d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J104" s="17" t="inlineStr">
@@ -15191,52 +15431,52 @@
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
-      <c r="B105" s="21" t="inlineStr">
-        <is>
-          <t>36C26126R0050</t>
-        </is>
-      </c>
-      <c r="C105" s="28" t="inlineStr">
-        <is>
-          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
-        </is>
-      </c>
-      <c r="D105" s="21" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
-      <c r="E105" s="21" t="inlineStr">
+      <c r="B105" s="23" t="inlineStr">
+        <is>
+          <t>W50S7X-26-B-A003</t>
+        </is>
+      </c>
+      <c r="C105" s="36" t="inlineStr">
+        <is>
+          <t>B16 PLC Replacement</t>
+        </is>
+      </c>
+      <c r="D105" s="23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F105" s="21" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G105" s="21" t="inlineStr">
-        <is>
-          <t>$5.0M</t>
-        </is>
-      </c>
-      <c r="H105" s="21" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I105" s="21" t="inlineStr">
-        <is>
-          <t>8d</t>
-        </is>
-      </c>
-      <c r="J105" s="21" t="inlineStr">
+      <c r="F105" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t>$5.1M</t>
+        </is>
+      </c>
+      <c r="H105" s="23" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="I105" s="23" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="J105" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K105" s="42" t="inlineStr">
+      <c r="K105" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15245,22 +15485,22 @@
     <row r="106" ht="28" customHeight="1">
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>140P8526Q0083</t>
+          <t>GROUP1-24-R-W001</t>
         </is>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
+          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
         </is>
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
@@ -15270,17 +15510,17 @@
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$17.5M</t>
         </is>
       </c>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="J106" s="17" t="inlineStr">
@@ -15295,52 +15535,52 @@
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
-      <c r="B107" s="23" t="inlineStr">
-        <is>
-          <t>140P9726Q0046</t>
-        </is>
-      </c>
-      <c r="C107" s="36" t="inlineStr">
-        <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
-        </is>
-      </c>
-      <c r="D107" s="23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E107" s="23" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
+        <is>
+          <t>36C26126R0050</t>
+        </is>
+      </c>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F107" s="23" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H107" s="23" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I107" s="23" t="inlineStr">
-        <is>
-          <t>9d</t>
-        </is>
-      </c>
-      <c r="J107" s="23" t="inlineStr">
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>$5.0M</t>
+        </is>
+      </c>
+      <c r="H107" s="21" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I107" s="21" t="inlineStr">
+        <is>
+          <t>8d</t>
+        </is>
+      </c>
+      <c r="J107" s="21" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K107" s="38" t="inlineStr">
+      <c r="K107" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15349,22 +15589,22 @@
     <row r="108" ht="28" customHeight="1">
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>W50S85-26-B-A007</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
@@ -15379,12 +15619,12 @@
       </c>
       <c r="H108" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="J108" s="17" t="inlineStr">
@@ -15399,52 +15639,52 @@
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
-      <c r="B109" s="21" t="inlineStr">
-        <is>
-          <t>36C24726Q0610</t>
-        </is>
-      </c>
-      <c r="C109" s="28" t="inlineStr">
-        <is>
-          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
-        </is>
-      </c>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>Columbia, South Carolina</t>
-        </is>
-      </c>
-      <c r="E109" s="21" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F109" s="21" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G109" s="21" t="inlineStr">
-        <is>
-          <t>$47.0M</t>
-        </is>
-      </c>
-      <c r="H109" s="21" t="inlineStr">
-        <is>
-          <t>Jul 01, 2026</t>
-        </is>
-      </c>
-      <c r="I109" s="21" t="inlineStr">
-        <is>
-          <t>15d</t>
-        </is>
-      </c>
-      <c r="J109" s="21" t="inlineStr">
+      <c r="B109" s="23" t="inlineStr">
+        <is>
+          <t>140P9726Q0046</t>
+        </is>
+      </c>
+      <c r="C109" s="36" t="inlineStr">
+        <is>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+        </is>
+      </c>
+      <c r="D109" s="23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E109" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F109" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H109" s="23" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026</t>
+        </is>
+      </c>
+      <c r="I109" s="23" t="inlineStr">
+        <is>
+          <t>9d</t>
+        </is>
+      </c>
+      <c r="J109" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K109" s="42" t="inlineStr">
+      <c r="K109" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15453,22 +15693,22 @@
     <row r="110" ht="28" customHeight="1">
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
+          <t>W50S85-26-B-A007</t>
         </is>
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>Repair Hush House Concrete B3857</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F110" s="17" t="inlineStr">
@@ -15478,17 +15718,17 @@
       </c>
       <c r="G110" s="17" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="J110" s="17" t="inlineStr">
@@ -15505,12 +15745,12 @@
     <row r="111" ht="28" customHeight="1">
       <c r="B111" s="23" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>W912DR26BA007</t>
         </is>
       </c>
       <c r="C111" s="36" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
         </is>
       </c>
       <c r="D111" s="23" t="inlineStr">
@@ -15520,139 +15760,139 @@
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t>$3.0M</t>
+        </is>
+      </c>
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I111" s="23" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="J111" s="23" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K111" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="B112" s="21" t="inlineStr">
+        <is>
+          <t>36C24726Q0610</t>
+        </is>
+      </c>
+      <c r="C112" s="28" t="inlineStr">
+        <is>
+          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
+        </is>
+      </c>
+      <c r="D112" s="21" t="inlineStr">
+        <is>
+          <t>Columbia, South Carolina</t>
+        </is>
+      </c>
+      <c r="E112" s="21" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G112" s="21" t="inlineStr">
+        <is>
+          <t>$47.0M</t>
+        </is>
+      </c>
+      <c r="H112" s="21" t="inlineStr">
+        <is>
+          <t>Jul 01, 2026</t>
+        </is>
+      </c>
+      <c r="I112" s="21" t="inlineStr">
+        <is>
+          <t>15d</t>
+        </is>
+      </c>
+      <c r="J112" s="21" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K112" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
+        </is>
+      </c>
+      <c r="C113" s="36" t="inlineStr">
+        <is>
+          <t>Repair Hush House Concrete B3857</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E113" s="23" t="inlineStr">
+        <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F111" s="23" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G111" s="23" t="inlineStr">
-        <is>
-          <t>$12.9M</t>
-        </is>
-      </c>
-      <c r="H111" s="23" t="inlineStr">
-        <is>
-          <t>Jul 07, 2026</t>
-        </is>
-      </c>
-      <c r="I111" s="23" t="inlineStr">
-        <is>
-          <t>21d</t>
-        </is>
-      </c>
-      <c r="J111" s="23" t="inlineStr">
+      <c r="F113" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t>$23.0M</t>
+        </is>
+      </c>
+      <c r="H113" s="23" t="inlineStr">
+        <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="I113" s="23" t="inlineStr">
+        <is>
+          <t>16d</t>
+        </is>
+      </c>
+      <c r="J113" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K111" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="B112" s="17" t="inlineStr">
-        <is>
-          <t>W9128F26BA019</t>
-        </is>
-      </c>
-      <c r="C112" s="33" t="inlineStr">
-        <is>
-          <t>Oahe IDCC Road Maintenance 2026</t>
-        </is>
-      </c>
-      <c r="D112" s="17" t="inlineStr">
-        <is>
-          <t>Fort Pierre, South Dakota</t>
-        </is>
-      </c>
-      <c r="E112" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F112" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>$21.5M</t>
-        </is>
-      </c>
-      <c r="H112" s="17" t="inlineStr">
-        <is>
-          <t>Jul 07, 2026</t>
-        </is>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
-        <is>
-          <t>21d</t>
-        </is>
-      </c>
-      <c r="J112" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K112" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="28" customHeight="1">
-      <c r="B113" s="21" t="inlineStr">
-        <is>
-          <t>36C24626R0067</t>
-        </is>
-      </c>
-      <c r="C113" s="28" t="inlineStr">
-        <is>
-          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
-        </is>
-      </c>
-      <c r="D113" s="21" t="inlineStr">
-        <is>
-          <t>Hampton, Virginia</t>
-        </is>
-      </c>
-      <c r="E113" s="21" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F113" s="21" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G113" s="21" t="inlineStr">
-        <is>
-          <t>$7.0M</t>
-        </is>
-      </c>
-      <c r="H113" s="21" t="inlineStr">
-        <is>
-          <t>Jul 13, 2026</t>
-        </is>
-      </c>
-      <c r="I113" s="21" t="inlineStr">
-        <is>
-          <t>27d</t>
-        </is>
-      </c>
-      <c r="J113" s="21" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K113" s="42" t="inlineStr">
+      <c r="K113" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15661,12 +15901,12 @@
     <row r="114" ht="28" customHeight="1">
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>140L2626R0004</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="D114" s="17" t="inlineStr">
@@ -15676,7 +15916,7 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
@@ -15686,17 +15926,17 @@
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="H114" s="17" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 07, 2026</t>
         </is>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="J114" s="17" t="inlineStr">
@@ -15713,22 +15953,22 @@
     <row r="115" ht="28" customHeight="1">
       <c r="B115" s="23" t="inlineStr">
         <is>
-          <t>140L2626Q0032</t>
+          <t>W9128F26BA019</t>
         </is>
       </c>
       <c r="C115" s="36" t="inlineStr">
         <is>
-          <t>Y--Indian Springs Vault Toilet</t>
+          <t>Oahe IDCC Road Maintenance 2026</t>
         </is>
       </c>
       <c r="D115" s="23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Fort Pierre, South Dakota</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
@@ -15738,77 +15978,77 @@
       </c>
       <c r="G115" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$21.5M</t>
         </is>
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
+          <t>Jul 07, 2026</t>
+        </is>
+      </c>
+      <c r="I115" s="23" t="inlineStr">
+        <is>
+          <t>21d</t>
+        </is>
+      </c>
+      <c r="J115" s="23" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K115" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="B116" s="21" t="inlineStr">
+        <is>
+          <t>36C24626R0067</t>
+        </is>
+      </c>
+      <c r="C116" s="28" t="inlineStr">
+        <is>
+          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+        </is>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
+        <is>
+          <t>Hampton, Virginia</t>
+        </is>
+      </c>
+      <c r="E116" s="21" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F116" s="21" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G116" s="21" t="inlineStr">
+        <is>
+          <t>$7.0M</t>
+        </is>
+      </c>
+      <c r="H116" s="21" t="inlineStr">
+        <is>
           <t>Jul 13, 2026</t>
         </is>
       </c>
-      <c r="I115" s="23" t="inlineStr">
+      <c r="I116" s="21" t="inlineStr">
         <is>
           <t>27d</t>
         </is>
       </c>
-      <c r="J115" s="23" t="inlineStr">
+      <c r="J116" s="21" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K115" s="38" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="B116" s="17" t="inlineStr">
-        <is>
-          <t>89503426BWA000068</t>
-        </is>
-      </c>
-      <c r="C116" s="33" t="inlineStr">
-        <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
-        </is>
-      </c>
-      <c r="D116" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E116" s="17" t="inlineStr">
-        <is>
-          <t>237130</t>
-        </is>
-      </c>
-      <c r="F116" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H116" s="17" t="inlineStr">
-        <is>
-          <t>Jul 15, 2026</t>
-        </is>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
-        <is>
-          <t>29d</t>
-        </is>
-      </c>
-      <c r="J116" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K116" s="35" t="inlineStr">
+      <c r="K116" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15817,22 +16057,22 @@
     <row r="117" ht="28" customHeight="1">
       <c r="B117" s="23" t="inlineStr">
         <is>
-          <t>W912EE26RA015</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C117" s="36" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D117" s="23" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
@@ -15847,12 +16087,12 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I117" s="23" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J117" s="23" t="inlineStr">
@@ -15869,12 +16109,12 @@
     <row r="118" ht="28" customHeight="1">
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>Y--Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D118" s="17" t="inlineStr">
@@ -15884,7 +16124,7 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
@@ -15899,12 +16139,12 @@
       </c>
       <c r="H118" s="17" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J118" s="17" t="inlineStr">
@@ -15921,22 +16161,22 @@
     <row r="119" ht="28" customHeight="1">
       <c r="B119" s="23" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C119" s="36" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D119" s="23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
@@ -15951,12 +16191,12 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I119" s="23" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J119" s="23" t="inlineStr">
@@ -15973,12 +16213,12 @@
     <row r="120" ht="28" customHeight="1">
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D120" s="17" t="inlineStr">
@@ -15988,7 +16228,7 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
@@ -16003,12 +16243,12 @@
       </c>
       <c r="H120" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
-          <t>38d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J120" s="17" t="inlineStr">
@@ -16025,12 +16265,12 @@
     <row r="121" ht="28" customHeight="1">
       <c r="B121" s="23" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C121" s="36" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D121" s="23" t="inlineStr">
@@ -16055,12 +16295,12 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I121" s="23" t="inlineStr">
         <is>
-          <t>38d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J121" s="23" t="inlineStr">
@@ -16077,12 +16317,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D122" s="17" t="inlineStr">
@@ -16129,12 +16369,12 @@
     <row r="123" ht="28" customHeight="1">
       <c r="B123" s="23" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C123" s="36" t="inlineStr">
         <is>
-          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D123" s="23" t="inlineStr">
@@ -16144,7 +16384,7 @@
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
@@ -16154,17 +16394,17 @@
       </c>
       <c r="G123" s="23" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I123" s="23" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>38d</t>
         </is>
       </c>
       <c r="J123" s="23" t="inlineStr">
@@ -16181,12 +16421,12 @@
     <row r="124" ht="28" customHeight="1">
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>140L3726R0006</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C124" s="33" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
@@ -16196,7 +16436,7 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
@@ -16206,17 +16446,17 @@
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H124" s="17" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
-          <t>73d</t>
+          <t>38d</t>
         </is>
       </c>
       <c r="J124" s="17" t="inlineStr">
@@ -16233,12 +16473,12 @@
     <row r="125" ht="28" customHeight="1">
       <c r="B125" s="23" t="inlineStr">
         <is>
-          <t>W912BU26BA026</t>
+          <t>140FGA26R0024</t>
         </is>
       </c>
       <c r="C125" s="36" t="inlineStr">
         <is>
-          <t>Absecon Island Outfalls Repair</t>
+          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
         </is>
       </c>
       <c r="D125" s="23" t="inlineStr">
@@ -16248,7 +16488,7 @@
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
@@ -16258,17 +16498,17 @@
       </c>
       <c r="G125" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="I125" s="23" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="J125" s="23" t="inlineStr">
@@ -16285,102 +16525,102 @@
     <row r="126" ht="28" customHeight="1">
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>75H70126R00029</t>
         </is>
       </c>
       <c r="C126" s="33" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
+          <t>Pine Ridge, South Dakota</t>
+        </is>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
+        <is>
+          <t>$3.0M</t>
+        </is>
+      </c>
+      <c r="H126" s="17" t="inlineStr">
+        <is>
+          <t>Jul 31, 2026</t>
+        </is>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>45d</t>
+        </is>
+      </c>
+      <c r="J126" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K126" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="B127" s="23" t="inlineStr">
+        <is>
+          <t>140L3726R0006</t>
+        </is>
+      </c>
+      <c r="C127" s="36" t="inlineStr">
+        <is>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+        </is>
+      </c>
+      <c r="D127" s="23" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E126" s="17" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F126" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H126" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I126" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="17" t="inlineStr">
+      <c r="E127" s="23" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F127" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>$19.0M</t>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="I127" s="23" t="inlineStr">
+        <is>
+          <t>73d</t>
+        </is>
+      </c>
+      <c r="J127" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K126" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="28" customHeight="1">
-      <c r="B127" s="21" t="inlineStr">
-        <is>
-          <t>36C25726B0007</t>
-        </is>
-      </c>
-      <c r="C127" s="28" t="inlineStr">
-        <is>
-          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
-        </is>
-      </c>
-      <c r="D127" s="21" t="inlineStr">
-        <is>
-          <t>Waco, Texas</t>
-        </is>
-      </c>
-      <c r="E127" s="21" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F127" s="21" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G127" s="21" t="inlineStr">
-        <is>
-          <t>$2.5B</t>
-        </is>
-      </c>
-      <c r="H127" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I127" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J127" s="21" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K127" s="42" t="inlineStr">
+      <c r="K127" s="38" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16389,12 +16629,12 @@
     <row r="128" ht="28" customHeight="1">
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>W912BU26BA026</t>
         </is>
       </c>
       <c r="C128" s="33" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Absecon Island Outfalls Repair</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
@@ -16419,12 +16659,12 @@
       </c>
       <c r="H128" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 16, 2026</t>
         </is>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J128" s="17" t="inlineStr">
@@ -16441,12 +16681,12 @@
     <row r="129" ht="28" customHeight="1">
       <c r="B129" s="23" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C129" s="36" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D129" s="23" t="inlineStr">
@@ -16456,7 +16696,7 @@
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
@@ -16491,52 +16731,52 @@
       </c>
     </row>
     <row r="130" ht="28" customHeight="1">
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>W912WJ26QA119</t>
-        </is>
-      </c>
-      <c r="C130" s="33" t="inlineStr">
-        <is>
-          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
-        </is>
-      </c>
-      <c r="D130" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E130" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F130" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G130" s="17" t="inlineStr">
-        <is>
-          <t>$175K</t>
-        </is>
-      </c>
-      <c r="H130" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I130" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J130" s="17" t="inlineStr">
+      <c r="B130" s="21" t="inlineStr">
+        <is>
+          <t>36C25726B0007</t>
+        </is>
+      </c>
+      <c r="C130" s="28" t="inlineStr">
+        <is>
+          <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
+        </is>
+      </c>
+      <c r="D130" s="21" t="inlineStr">
+        <is>
+          <t>Waco, Texas</t>
+        </is>
+      </c>
+      <c r="E130" s="21" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G130" s="21" t="inlineStr">
+        <is>
+          <t>$2.5B</t>
+        </is>
+      </c>
+      <c r="H130" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J130" s="21" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K130" s="35" t="inlineStr">
+      <c r="K130" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16545,17 +16785,17 @@
     <row r="131" ht="28" customHeight="1">
       <c r="B131" s="23" t="inlineStr">
         <is>
-          <t>W911WN26BA008</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C131" s="36" t="inlineStr">
         <is>
-          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D131" s="23" t="inlineStr">
         <is>
-          <t>Saltsburg, Pennsylvania</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
@@ -16570,7 +16810,7 @@
       </c>
       <c r="G131" s="23" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H131" s="23" t="inlineStr">
@@ -16597,12 +16837,12 @@
     <row r="132" ht="28" customHeight="1">
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C132" s="33" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D132" s="17" t="inlineStr">
@@ -16622,7 +16862,7 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
@@ -16649,22 +16889,22 @@
     <row r="133" ht="28" customHeight="1">
       <c r="B133" s="23" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>W912WJ26QA119</t>
         </is>
       </c>
       <c r="C133" s="36" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>Storage Building Parking Lot Installation and Paving, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D133" s="23" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
@@ -16674,7 +16914,7 @@
       </c>
       <c r="G133" s="23" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H133" s="23" t="inlineStr">
@@ -16701,22 +16941,22 @@
     <row r="134" ht="28" customHeight="1">
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>W911WN26BA008</t>
         </is>
       </c>
       <c r="C134" s="33" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
         </is>
       </c>
       <c r="D134" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Saltsburg, Pennsylvania</t>
         </is>
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
@@ -16726,7 +16966,7 @@
       </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H134" s="17" t="inlineStr">
@@ -16753,12 +16993,12 @@
     <row r="135" ht="28" customHeight="1">
       <c r="B135" s="23" t="inlineStr">
         <is>
-          <t>W9128F26RA107</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C135" s="36" t="inlineStr">
         <is>
-          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D135" s="23" t="inlineStr">
@@ -16768,7 +17008,7 @@
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
@@ -16778,7 +17018,7 @@
       </c>
       <c r="G135" s="23" t="inlineStr">
         <is>
-          <t>$30.0M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H135" s="23" t="inlineStr">
@@ -16803,52 +17043,52 @@
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
-      <c r="B136" s="21" t="inlineStr">
-        <is>
-          <t>36C24226B0057</t>
-        </is>
-      </c>
-      <c r="C136" s="28" t="inlineStr">
-        <is>
-          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
-        </is>
-      </c>
-      <c r="D136" s="21" t="inlineStr">
-        <is>
-          <t>Buffalo, New York</t>
-        </is>
-      </c>
-      <c r="E136" s="21" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="F136" s="21" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G136" s="21" t="inlineStr">
-        <is>
-          <t>$16.2M</t>
-        </is>
-      </c>
-      <c r="H136" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I136" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J136" s="21" t="inlineStr">
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>75H70126R00030</t>
+        </is>
+      </c>
+      <c r="C136" s="33" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G136" s="17" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="H136" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J136" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K136" s="42" t="inlineStr">
+      <c r="K136" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -16857,17 +17097,17 @@
     <row r="137" ht="28" customHeight="1">
       <c r="B137" s="23" t="inlineStr">
         <is>
-          <t>140P6326B0008</t>
+          <t>140FGA26R0028</t>
         </is>
       </c>
       <c r="C137" s="36" t="inlineStr">
         <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
         </is>
       </c>
       <c r="D137" s="23" t="inlineStr">
         <is>
-          <t>Medora, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
@@ -16882,7 +17122,7 @@
       </c>
       <c r="G137" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="H137" s="23" t="inlineStr">
@@ -16909,12 +17149,12 @@
     <row r="138" ht="28" customHeight="1">
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>12445526Q0069</t>
+          <t>W9128F26RA107</t>
         </is>
       </c>
       <c r="C138" s="33" t="inlineStr">
         <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+          <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
         </is>
       </c>
       <c r="D138" s="17" t="inlineStr">
@@ -16934,22 +17174,22 @@
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
-          <t>$25K</t>
+          <t>$30.0M</t>
         </is>
       </c>
       <c r="H138" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
-          <t>8d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J138" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K138" s="35" t="inlineStr">
@@ -16959,52 +17199,52 @@
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
-      <c r="B139" s="23" t="inlineStr">
-        <is>
-          <t>SP470525R002026</t>
-        </is>
-      </c>
-      <c r="C139" s="36" t="inlineStr">
-        <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
-        </is>
-      </c>
-      <c r="D139" s="23" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E139" s="23" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F139" s="23" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G139" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H139" s="23" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I139" s="23" t="inlineStr">
-        <is>
-          <t>14d</t>
-        </is>
-      </c>
-      <c r="J139" s="23" t="inlineStr">
-        <is>
-          <t>Special Notice</t>
-        </is>
-      </c>
-      <c r="K139" s="38" t="inlineStr">
+      <c r="B139" s="21" t="inlineStr">
+        <is>
+          <t>36C24226B0057</t>
+        </is>
+      </c>
+      <c r="C139" s="28" t="inlineStr">
+        <is>
+          <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
+        </is>
+      </c>
+      <c r="D139" s="21" t="inlineStr">
+        <is>
+          <t>Buffalo, New York</t>
+        </is>
+      </c>
+      <c r="E139" s="21" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G139" s="21" t="inlineStr">
+        <is>
+          <t>$16.2M</t>
+        </is>
+      </c>
+      <c r="H139" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I139" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J139" s="21" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K139" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -17013,57 +17253,265 @@
     <row r="140" ht="28" customHeight="1">
       <c r="B140" s="17" t="inlineStr">
         <is>
+          <t>140P6326B0008</t>
+        </is>
+      </c>
+      <c r="C140" s="33" t="inlineStr">
+        <is>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>Medora, North Dakota</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G140" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H140" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J140" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K140" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="B141" s="23" t="inlineStr">
+        <is>
+          <t>W912DQ26QA063</t>
+        </is>
+      </c>
+      <c r="C141" s="36" t="inlineStr">
+        <is>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+        </is>
+      </c>
+      <c r="D141" s="23" t="inlineStr">
+        <is>
+          <t>Stockton, Missouri</t>
+        </is>
+      </c>
+      <c r="E141" s="23" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F141" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I141" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="23" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K141" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="28" customHeight="1">
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>12445526Q0069</t>
+        </is>
+      </c>
+      <c r="C142" s="33" t="inlineStr">
+        <is>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>8d</t>
+        </is>
+      </c>
+      <c r="J142" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K142" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="B143" s="23" t="inlineStr">
+        <is>
+          <t>SP470525R002026</t>
+        </is>
+      </c>
+      <c r="C143" s="36" t="inlineStr">
+        <is>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+        </is>
+      </c>
+      <c r="D143" s="23" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E143" s="23" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F143" s="23" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="23" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I143" s="23" t="inlineStr">
+        <is>
+          <t>14d</t>
+        </is>
+      </c>
+      <c r="J143" s="23" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K143" s="38" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="B144" s="17" t="inlineStr">
+        <is>
           <t>W9127826RA025</t>
         </is>
       </c>
-      <c r="C140" s="33" t="inlineStr">
+      <c r="C144" s="33" t="inlineStr">
         <is>
           <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
-      <c r="D140" s="17" t="inlineStr">
+      <c r="D144" s="17" t="inlineStr">
         <is>
           <t>Cape Canaveral, Florida</t>
         </is>
       </c>
-      <c r="E140" s="17" t="inlineStr">
+      <c r="E144" s="17" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F140" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G140" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H140" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J140" s="17" t="inlineStr">
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="17" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="K140" s="35" t="inlineStr">
+      <c r="K144" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K140"/>
+  <autoFilter ref="B5:K144"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -17204,6 +17652,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17216,7 +17668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K76"/>
+  <dimension ref="B2:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -17244,7 +17696,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="47" t="inlineStr">
         <is>
-          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  71 records  (14 SDVOSB)  ·  June 15, 2026</t>
+          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  74 records  (14 SDVOSB)  ·  June 15, 2026</t>
         </is>
       </c>
     </row>
@@ -20060,12 +20512,12 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D59" s="56" t="inlineStr">
@@ -20117,7 +20569,7 @@
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -20137,12 +20589,12 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
@@ -20164,17 +20616,17 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable B230 to B9511</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D61" s="56" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E61" s="56" t="inlineStr">
@@ -20189,12 +20641,12 @@
       </c>
       <c r="G61" s="56" t="inlineStr">
         <is>
-          <t>Jun 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H61" s="56" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="I61" s="56" t="inlineStr">
@@ -20202,9 +20654,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J61" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J61" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K61" s="57" t="inlineStr">
@@ -20216,17 +20668,17 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>Z--WACO Emergency Generator</t>
+          <t>Water Tank Storage</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Waco, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -20236,27 +20688,27 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>$62K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Jun 18, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="J62" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="J62" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K62" s="35" t="inlineStr">
@@ -20273,12 +20725,12 @@
       </c>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>J065--Variable Frequency Drive Maintenance</t>
+          <t>Fiber Optic Cable B230 to B9511</t>
         </is>
       </c>
       <c r="D63" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="E63" s="56" t="inlineStr">
@@ -20293,17 +20745,17 @@
       </c>
       <c r="G63" s="56" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 16, 2026</t>
         </is>
       </c>
       <c r="H63" s="56" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I63" s="56" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="J63" s="18" t="inlineStr">
@@ -20320,17 +20772,17 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
+          <t>Z--WACO Emergency Generator</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>Baltimore, MD</t>
+          <t>Waco, Texas</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -20340,17 +20792,17 @@
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$62K</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>Jun 22, 2026</t>
+          <t>Jun 18, 2026</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
@@ -20372,17 +20824,17 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="54" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>J065--Variable Frequency Drive Maintenance</t>
         </is>
       </c>
       <c r="D65" s="56" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E65" s="56" t="inlineStr">
@@ -20392,7 +20844,7 @@
       </c>
       <c r="F65" s="56" t="inlineStr">
         <is>
-          <t>$47.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="56" t="inlineStr">
@@ -20424,17 +20876,17 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>J045--PREVENTIVE MAINTENANCE &amp; CLEANING- 41 DX HVAC</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Baltimore, MD</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -20444,17 +20896,17 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
@@ -20476,17 +20928,17 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D67" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E67" s="56" t="inlineStr">
@@ -20496,17 +20948,17 @@
       </c>
       <c r="F67" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="G67" s="56" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 22, 2026</t>
         </is>
       </c>
       <c r="H67" s="56" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="I67" s="56" t="inlineStr">
@@ -20528,17 +20980,17 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -20548,17 +21000,17 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
@@ -20580,12 +21032,12 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="54" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>Y--Beresford Substation Stage 11, South Dakota</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D69" s="56" t="inlineStr">
@@ -20605,12 +21057,12 @@
       </c>
       <c r="G69" s="56" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="H69" s="56" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="I69" s="56" t="inlineStr">
@@ -20618,9 +21070,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J69" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K69" s="57" t="inlineStr">
@@ -20632,17 +21084,17 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -20657,12 +21109,12 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>14d</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
@@ -20670,9 +21122,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J70" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+      <c r="J70" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K70" s="35" t="inlineStr">
@@ -20684,17 +21136,17 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C71" s="55" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D71" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E71" s="56" t="inlineStr">
@@ -20709,12 +21161,12 @@
       </c>
       <c r="G71" s="56" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H71" s="56" t="inlineStr">
         <is>
-          <t>38d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="I71" s="56" t="inlineStr">
@@ -20722,9 +21174,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J71" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J71" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K71" s="57" t="inlineStr">
@@ -20741,7 +21193,7 @@
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
@@ -20788,12 +21240,12 @@
     <row r="73" ht="28" customHeight="1">
       <c r="B73" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C73" s="55" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D73" s="56" t="inlineStr">
@@ -20808,17 +21260,17 @@
       </c>
       <c r="F73" s="56" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="56" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H73" s="56" t="inlineStr">
         <is>
-          <t>73d</t>
+          <t>38d</t>
         </is>
       </c>
       <c r="I73" s="56" t="inlineStr">
@@ -20840,17 +21292,17 @@
     <row r="74" ht="28" customHeight="1">
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -20860,17 +21312,17 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45d</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
@@ -20880,7 +21332,7 @@
       </c>
       <c r="J74" s="44" t="inlineStr">
         <is>
-          <t>Pre-Sol</t>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K74" s="35" t="inlineStr">
@@ -20892,17 +21344,17 @@
     <row r="75" ht="28" customHeight="1">
       <c r="B75" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C75" s="55" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D75" s="56" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E75" s="56" t="inlineStr">
@@ -20912,17 +21364,17 @@
       </c>
       <c r="F75" s="56" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G75" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H75" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73d</t>
         </is>
       </c>
       <c r="I75" s="56" t="inlineStr">
@@ -20932,7 +21384,7 @@
       </c>
       <c r="J75" s="44" t="inlineStr">
         <is>
-          <t>Pre-Sol</t>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K75" s="57" t="inlineStr">
@@ -20944,57 +21396,213 @@
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="16" t="inlineStr">
         <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="inlineStr">
+        <is>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J76" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K76" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="B77" s="54" t="inlineStr">
+        <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C77" s="55" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="D77" s="56" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E77" s="56" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F77" s="56" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="G77" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="56" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J77" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K77" s="57" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>237110 — Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="inlineStr">
+        <is>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Stockton, Missouri</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J78" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K78" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="B79" s="54" t="inlineStr">
+        <is>
           <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
-      <c r="C76" s="33" t="inlineStr">
+      <c r="C79" s="55" t="inlineStr">
         <is>
           <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D79" s="56" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E76" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="17" t="inlineStr">
+      <c r="E79" s="56" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F79" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="56" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="H76" s="17" t="inlineStr">
+      <c r="H79" s="56" t="inlineStr">
         <is>
           <t>14d</t>
         </is>
       </c>
-      <c r="I76" s="17" t="inlineStr">
+      <c r="I79" s="56" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="J76" s="18" t="inlineStr">
+      <c r="J79" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="K76" s="35" t="inlineStr">
+      <c r="K79" s="57" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K76"/>
+  <autoFilter ref="B5:K79"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -21071,6 +21679,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
